--- a/docs/机场可用性清单-2026-10-17.xlsx
+++ b/docs/机场可用性清单-2026-10-17.xlsx
@@ -7,15 +7,18 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="机场清单" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域名全集" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="推荐站画像" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-22 09-25" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="机场清单" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域名全集" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="推荐站画像" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'机场清单'!$A$1:$R$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'域名全集'!$A$1:$F$380</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'推荐站画像'!$A$1:$I$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026-10-22 09-25'!$A$1:$K$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'机场清单'!$A$1:$R$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'域名全集'!$A$1:$F$380</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'推荐站画像'!$A$1:$I$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,8 +46,20 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +86,11 @@
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7E6E6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -84,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -97,6 +117,25 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -462,6 +501,2743 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>机场监控总览（每次运行追加一行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>机场数</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>✅正常</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>⏳抖动</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>❌异常</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>快照节点</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
+        <is>
+          <t>可导出</t>
+        </is>
+      </c>
+      <c r="H3" s="16" t="inlineStr">
+        <is>
+          <t>订阅成功/失败</t>
+        </is>
+      </c>
+      <c r="I3" s="16" t="inlineStr">
+        <is>
+          <t>耗时(秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-22 09-25</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>47</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2112</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1446</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>29/16</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>3439.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>怎么读：</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1. 每跑一次监控，工作簿里新增一张以「本轮结束时间」命名的表，基础信息+本轮状态都在里面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2. 「机场清单」只放基础信息（18 列），不再往右加列；本页是历次运行的一行摘要。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3. 快照节点=本轮抓到的全部条目（含只有 IP:端口 的残片）；可导出节点=能生成 Clash/订阅配置的条数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>4. 客户端型机场（fastlink/speedcat/dovex/letsvpn/quqiuquan/lingdian/ssrdog）的节点几小时就轮换，导出配置有保鲜期。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>5. 套餐过期后订阅仍可能出节点（qiangda 就是这样），但随时会断。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>机场</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>基础状态</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>面板域名</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>获取方式</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>客户端版本</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>套餐到期</t>
+        </is>
+      </c>
+      <c r="G1" s="10" t="inlineStr">
+        <is>
+          <t>本轮状态</t>
+        </is>
+      </c>
+      <c r="H1" s="10" t="inlineStr">
+        <is>
+          <t>快照节点</t>
+        </is>
+      </c>
+      <c r="I1" s="10" t="inlineStr">
+        <is>
+          <t>可导出节点</t>
+        </is>
+      </c>
+      <c r="J1" s="10" t="inlineStr">
+        <is>
+          <t>卡在哪</t>
+        </is>
+      </c>
+      <c r="K1" s="10" t="inlineStr">
+        <is>
+          <t>需要你做什么</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>hhy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>app.nicehcloud.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>仅客户端(注册表无订阅)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>hhycenter 3.2.0@2026-08-07｜无需更新（面板挂不影响客户端）</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G2" s="11" t="inlineStr">
+        <is>
+          <t>✅ 正常</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>163</v>
+      </c>
+      <c r="I2" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>套餐到期+面板禁客户端：续费</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>letsvpn</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>letsvpn.world</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>仅客户端(常驻)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>LetsPRO 3.20.0@2026-06-02｜keep_alive 进程当前不在运行——下一轮(23:28)观察是否掉 0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>❌ 异常</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>无订阅链接，依赖 LetsPRO 客户端；本轮 LetsPRO.exe 未运行 → 0 节点（10-19 曾有 153 节点）</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>启动 LetsPRO 保持登录+连接</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>fastlink</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>fastlink.so</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>仅客户端(注册表无订阅)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>FastLink 3.1.8@2026-07-16｜无需更新</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>✅ 正常</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>167</v>
+      </c>
+      <c r="I4" t="n">
+        <v>39</v>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ayucloud</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ayucloud.nl</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>仅订阅</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>⏳ 抖动</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>141</v>
+      </c>
+      <c r="I5" t="n">
+        <v>141</v>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>订阅成功但本轮没产出节点（瞬时抖动），下轮自动重试</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>lingdian</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>www.0dy4.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>仅客户端(注册表无订阅)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0dcloudCore(无版本号)@2026-06-02｜正常</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>❌ 异常</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>订阅 HTTP 504 网关超时；面板非 SSPanel 结构；客户端 0dcloudCore 本轮 0 节点——订阅/面板/客户端三通路全断；历史最后一次有节点：2026-10-19 08:58（126 个）</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>机场侧 504 整站故障，等修</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cherryvpn</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>cherryvpn.net</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>仅订阅</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>无到期日</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>✅ 正常</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>123</v>
+      </c>
+      <c r="I7" t="n">
+        <v>123</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>bygcloud</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>www.bygcloud.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>仅订阅</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2027-09-09</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>✅ 正常</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>104</v>
+      </c>
+      <c r="I8" t="n">
+        <v>104</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>maxiong</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>maxiong.co</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>仅订阅(客户端装而未跑)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Dapan 已安装未使用（订阅活，暂不需要）</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-12-24</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>✅ 正常</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>99</v>
+      </c>
+      <c r="I9" t="n">
+        <v>99</v>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>flybar</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>8.163.57.84:12</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>仅订阅</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>无到期日</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>✅ 正常</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>88</v>
+      </c>
+      <c r="I10" t="n">
+        <v>42</v>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>qiangda</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>wx.xn--wbsz85a2a.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>仅订阅</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>❌ 异常</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>86</v>
+      </c>
+      <c r="I11" t="n">
+        <v>86</v>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>订阅连接被远端中断（10054）；面板 TLS 握手失败；套餐 2026-09-26 到期（-26 天）；历史最后一次有节点：2026-10-19 08:58（86 个）</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>过期 26 天：续费或下线</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>dovex</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>dovex.cc</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>仅客户端(注册表无订阅)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>DOVE 2.1.7@2026-09-03｜官网产品线 2.0 系，属当前线，无需更新</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>❌ 异常</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>无订阅链接，依赖 dove-core 客户端；本轮客户端扫描 0 节点（10-19 曾有 85 节点）；面板 WHMCS 登录失败</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>启动 dove-core 客户端并登录</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>speedcat</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>scesa.apiv2.a047.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>仅客户端(注册表无订阅)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SpeedCat 3.0.3@2026-05-01｜本地最老客户端之一，但 12 轮扫描全成功；真实面板 w06.scweba09.cc 需登录才能看下载页</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>✅ 正常</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>83</v>
+      </c>
+      <c r="I13" t="n">
+        <v>50</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>xm999</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>mmuser.mmget.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>仅订阅</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>❌ 异常</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>77</v>
+      </c>
+      <c r="I14" t="n">
+        <v>77</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>订阅主机不可达（多次重试）；面板 v2board 返回 522（CF 回源超时）；套餐仍剩 69 天；历史最后一次有节点：2026-10-19 08:58（77 个）</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>等机场修（522）或换新域名后给订阅地址</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>neko77</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>neko77.best</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>仅订阅</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>无到期日</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>✅ 正常</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>69</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>kuainiao</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>wwwwa.xn--123-x03fp95y.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>仅订阅</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>无到期日</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>❌ 异常</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>61</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>订阅连接被远端中断（10054）；面板登录被拒「邮箱或密码错误」（含官网发现的备用后台）；无额度记录；历史最后一次有节点：2026-10-19 08:58（61 个）</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>给新密码（面板报“邮箱或密码错误”）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>flyint</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>www.flyintpro.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>仅订阅</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>无到期日</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>✅ 正常</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>55</v>
+      </c>
+      <c r="I17" t="n">
+        <v>55</v>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>mitce</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>mitce.io</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>仅订阅</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2027-08-26</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>✅ 正常</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>39</v>
+      </c>
+      <c r="I18" t="n">
+        <v>39</v>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>quqiuquan</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>backendapi.cniw4-dcc3vq.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>仅客户端(常驻)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>QQT 1.4.21@2026-08-18｜无需更新</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>⏳ 抖动</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>订阅成功但本轮没产出节点（瞬时抖动），下轮自动重试</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>启动 QQT 并登录连接</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>liangxin</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>xn--9kqz23b19z.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>仅订阅</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2027-08-26</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>✅ 正常</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>56</v>
+      </c>
+      <c r="I20" t="n">
+        <v>56</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ktm</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ktmcloud001.top</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>仅订阅</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2027-08-26</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>✅ 正常</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>55</v>
+      </c>
+      <c r="I21" t="n">
+        <v>55</v>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ssrdog</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>comsla-1.dog-sla01.store</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>仅客户端(注册表无订阅)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SSRDOG 1.1.2@2026-08-28｜无需更新</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>✅ 正常</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>56</v>
+      </c>
+      <c r="I22" t="n">
+        <v>36</v>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>jinglingxueyuan</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>info.riolu.icu</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>仅订阅</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2027-09-09</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>✅ 正常</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>51</v>
+      </c>
+      <c r="I23" t="n">
+        <v>51</v>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>oixcloud</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>oixcloud.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>仅订阅</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>❌ 异常</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>47</v>
+      </c>
+      <c r="I24" t="n">
+        <v>47</v>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>订阅 HTTP 403；面板登录报「页面已过期」；套餐 2026-09-16 到期（-36 天）；历史最后一次有节点：2026-10-19 08:58（47 个）</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>过期 36 天：续费或下线</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>feiniao</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>feiniaoyun.top</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>仅订阅</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>无到期日</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>⏳ 抖动</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>21</v>
+      </c>
+      <c r="I25" t="n">
+        <v>21</v>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>订阅成功但本轮没产出节点（瞬时抖动），下轮自动重试</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>selom</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>www.selom.xyz</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>仅订阅</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>无到期日</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>⏳ 抖动</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>37</v>
+      </c>
+      <c r="I26" t="n">
+        <v>37</v>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>订阅成功但本轮没产出节点（瞬时抖动），下轮自动重试</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>muniu-ninja</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>—未登记面板</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>本地静态清单(35 节点)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>❌ 异常</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>35</v>
+      </c>
+      <c r="I27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>无独立订阅链接（与 muniu 同一账号），数据靠 ../0701-muniu 客户端配置摄入；credentials.yaml 无此 slug，run.py all 从不拉取它，本轮仅被 rescan 重写，节点实际仍停在 10-19；历史最后一次有节点：2026-10-19 08:58（35 个</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>无独立订阅，跟 muniu 一起处理</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>feiniao_1</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1wuusumxb.fnyunkr.shop</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>仅订阅</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2027-08-26</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>✅ 正常</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>34</v>
+      </c>
+      <c r="I28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>mojie</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>mojie.app</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>仅订阅</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>无到期日</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>✅ 正常</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>34</v>
+      </c>
+      <c r="I29" t="n">
+        <v>34</v>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>velochron</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>api.9aero.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>仅客户端(velo_api 专用)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>nanocore@2026-09-12｜最新，无需更新</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>✅ 正常</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>34</v>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>客户端 1.2.5.3 → 1.3.3.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>applegame</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>apple5.applenet.link</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>仅订阅</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>⏳ 抖动</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" t="n">
+        <v>30</v>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>订阅成功但本轮没产出节点（瞬时抖动），下轮自动重试</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>dualnet</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ann.nextdual.net</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>仅订阅</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2027-01-29</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>✅ 正常</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>29</v>
+      </c>
+      <c r="I32" t="n">
+        <v>29</v>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>pkq</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>www.pkqcloudx.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>仅订阅</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2027-02-14</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>✅ 正常</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>28</v>
+      </c>
+      <c r="I33" t="n">
+        <v>28</v>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cloudnx</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>—未登记面板</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>仅订阅</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2027-01-23</t>
+        </is>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>✅ 正常</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>27</v>
+      </c>
+      <c r="I34" t="n">
+        <v>27</v>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>feiniao_2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>portal1.xlcc.plus</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>仅订阅</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>✅ 正常</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>25</v>
+      </c>
+      <c r="I35" t="n">
+        <v>25</v>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>no626</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>cloud.no626.net</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>仅订阅</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>无到期日</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>✅ 正常</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>24</v>
+      </c>
+      <c r="I36" t="n">
+        <v>24</v>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>everlife</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>cloud.evertheless.art</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>仅订阅</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>无到期日</t>
+        </is>
+      </c>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>⏳ 抖动</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>23</v>
+      </c>
+      <c r="I37" t="n">
+        <v>23</v>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>订阅成功但本轮没产出节点（瞬时抖动），下轮自动重试</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>hsyun</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>front.cvucqh.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>仅订阅</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="G38" s="11" t="inlineStr">
+        <is>
+          <t>✅ 正常</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>23</v>
+      </c>
+      <c r="I38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>bywave</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>u.bws.lol</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>仅订阅</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2027-06-30</t>
+        </is>
+      </c>
+      <c r="G39" s="13" t="inlineStr">
+        <is>
+          <t>❌ 异常</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>20</v>
+      </c>
+      <c r="I39" t="n">
+        <v>20</v>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>订阅 HTTP 404；面板 WHMCS 登录失败（未取到校验位）；5 个种子域名探测全部失败；套餐仍剩 251 天；历史最后一次有节点：2026-10-19 08:58（20 个）</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>手动拖滑块登录后台，把订阅地址发我</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>new-yiyuan</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>yiyuan.co</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>仅订阅</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2027-09-14</t>
+        </is>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>✅ 正常</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>18</v>
+      </c>
+      <c r="I40" t="n">
+        <v>18</v>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ss-id</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>qe.newssid.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>仅订阅</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2027-09-09</t>
+        </is>
+      </c>
+      <c r="G41" s="13" t="inlineStr">
+        <is>
+          <t>❌ 异常</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>15</v>
+      </c>
+      <c r="I41" t="n">
+        <v>15</v>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>订阅 HTTP 403；面板两条登录路径均失败；套餐仍剩 322 天；历史最后一次有节点：2026-10-19 08:58（15 个）</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>后台重新复制订阅地址发我（403）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>chaoyue</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>可用</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>www.chaoyue.shop</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>仅订阅</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2027-01-16</t>
+        </is>
+      </c>
+      <c r="G42" s="11" t="inlineStr">
+        <is>
+          <t>✅ 正常</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>14</v>
+      </c>
+      <c r="I42" t="n">
+        <v>14</v>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>wandacloud</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>观察</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>app.wandayun.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>仅客户端(订阅面板已死)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>wandacloud 2.2.792@2026-04-25｜最老客户端；登记面板已死无处下载新版——扫描路线暂活(7节点)，先不动</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>✅ 正常</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>7</v>
+      </c>
+      <c r="I43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>客户端 2.2.792 → 3.2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>wdy</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>观察</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>new.wdycenter.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>仅客户端(订阅死)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>wandacloud 2.2.792@2026-04-25｜同 wandacloud</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>无到期日</t>
+        </is>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>✅ 正常</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>6</v>
+      </c>
+      <c r="I44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>qingyunti</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>观察</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>qingyunti.org</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>仅客户端(注册表无订阅)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>QingyunLite 3.1.8@2026-07-16｜无需更新</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="11" t="inlineStr">
+        <is>
+          <t>✅ 正常</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>3</v>
+      </c>
+      <c r="I45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>浏览器登录后复制订阅地址发我（面板 403）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>jsqpro</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>不可用</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>registered.jsqpro.store</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>全断(订阅 0 节点×12轮)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
+        <is>
+          <t>❌ 异常</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>订阅 HTTP 500；面板 v2board/sspanel 两条登录路径均失败；套餐 2026-10-01 到期（-21 天，已停用）；历史最后一次有节点：2026-10-01 00:22（24 个）</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>过期 22 天：续费或下线</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>muniu</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>不可用</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>muniu.org</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>全断(订阅 0 节点×12轮)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>V-Ninja 安装目录已不存在（客户端已删，与全断一致）</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G47" s="13" t="inlineStr">
+        <is>
+          <t>❌ 异常</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>订阅（manual-url 路线）0 节点；客户端 clash-ninja-service 本轮 3 份快照均 0 节点；套餐 2026-07-17 到期（-97 天）</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>过期 97 天：续费或下线</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>yiyuan</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>不可用</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>69.63.197.45:6201</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>全断(订阅 0×12轮，面板活·换新订阅可复活)</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>—(无客户端)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>❌ 异常</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>订阅 HTTP 502；面板两条登录路径均失败；套餐 2025-10-21 到期且流量 100% 用尽（-366 天）；历史最后一次有节点：2026-09-27 12:11（95 个）</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>过期 366 天+流量用尽：建议下线</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>说明：快照节点=本轮抓到的全部条目（含只有 IP:端口 的残片）；可导出节点=能生成 Clash/订阅配置的条数。灰底=0 条。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K48"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:R48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -483,6 +3259,11 @@
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="52" customWidth="1" min="22" max="22"/>
+    <col width="44" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4584,7 +7365,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4717,7 +7498,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4792,7 +7573,6 @@
           <t>探测10-18; 推荐站:pianyijichang/haohaoyun</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4820,7 +7600,6 @@
           <t>推荐站:pianyijichang/haohaoyun</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4848,7 +7627,6 @@
           <t>探测10-18; 推荐站:pianyijichang/haohaoyun</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4876,7 +7654,6 @@
           <t>推荐站:pianyijichang/haohaoyun</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4904,7 +7681,6 @@
           <t>推荐站:pianyijichang/haohaoyun</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4922,13 +7698,11 @@
           <t>200 活</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>探测10-18; 推荐站:pianyijichang/haohaoyun</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4946,13 +7720,11 @@
           <t>502</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>凭证面板; 探测10-17; 推荐站:pianyijichang/haohaoyun</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4980,7 +7752,6 @@
           <t>探测10-18; 推荐站:pianyijichang/haohaoyun</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5008,7 +7779,6 @@
           <t>探测10-18; 推荐站:pianyijichang/haohaoyun</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5036,7 +7806,6 @@
           <t>探测10-18; 推荐站:pianyijichang/haohaoyun</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5064,7 +7833,6 @@
           <t>凭证面板; yaml官网; yaml域名表; 探测10-17</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5092,7 +7860,6 @@
           <t>推荐站:iplc/fastlink</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5120,7 +7887,6 @@
           <t>推荐站:iplc/fastlink</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5148,7 +7914,6 @@
           <t>推荐站:iplc/fastlink</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5176,7 +7941,6 @@
           <t>探测10-18; 推荐站:iplc/fastlink</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5204,7 +7968,6 @@
           <t>探测10-18; 推荐站:iplc/fastlink</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5232,7 +7995,6 @@
           <t>探测10-18; 推荐站:iplc/fastlink</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5260,7 +8022,6 @@
           <t>推荐站:iplc/fastlink</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5288,7 +8049,6 @@
           <t>推荐站:iplc/fastlink</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5316,7 +8076,6 @@
           <t>推荐站:iplc/fastlink</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5344,7 +8103,6 @@
           <t>推荐站:iplc/fastlink</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5372,7 +8130,6 @@
           <t>推荐站:iplc/fastlink</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5400,7 +8157,6 @@
           <t>凭证面板; 探测10-17</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5428,7 +8184,6 @@
           <t>探测10-18; 推荐站:iplc/fastlink</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5456,7 +8211,6 @@
           <t>探测10-18; 推荐站:iplc/fastlink</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5484,7 +8238,6 @@
           <t>推荐站:iplc/fastlink</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5512,7 +8265,6 @@
           <t>凭证面板; 探测10-17</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5540,7 +8292,6 @@
           <t>yaml域名表</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5568,7 +8319,6 @@
           <t>yaml域名表</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5596,7 +8346,6 @@
           <t>yaml域名表</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5624,7 +8373,6 @@
           <t>yaml域名表</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5652,7 +8400,6 @@
           <t>yaml域名表</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5680,7 +8427,6 @@
           <t>凭证面板; yaml面板; 探测10-17</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5708,7 +8454,6 @@
           <t>yaml域名表</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5736,7 +8481,6 @@
           <t>yaml域名表</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5764,7 +8508,6 @@
           <t>凭证面板; 探测10-17</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5792,7 +8535,6 @@
           <t>推荐站:iplc/bygcloud</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5820,7 +8562,6 @@
           <t>凭证面板; 探测10-17; 推荐站:iplc/bygcloud</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5848,7 +8589,6 @@
           <t>推荐站:iplc/bygcloud</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5876,7 +8616,6 @@
           <t>推荐站:iplc/bygcloud</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5904,7 +8643,6 @@
           <t>凭证面板; 探测10-17</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5932,7 +8670,6 @@
           <t>凭证面板; 探测10-17</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5950,7 +8687,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>凭证面板; 探测10-17</t>
@@ -5988,7 +8724,6 @@
           <t>yaml域名表</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6016,7 +8751,6 @@
           <t>凭证面板; 探测10-17</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6044,7 +8778,6 @@
           <t>yaml域名表</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6072,7 +8805,6 @@
           <t>yaml域名表</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6100,7 +8832,6 @@
           <t>探测10-18; 推荐站:iplc/shandianmao</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6128,7 +8859,6 @@
           <t>探测10-18; 推荐站:iplc/shandianmao</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6156,7 +8886,6 @@
           <t>推荐站:iplc/shandianmao</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6184,7 +8913,6 @@
           <t>推荐站:iplc/shandianmao</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6212,7 +8940,6 @@
           <t>探测10-18; 推荐站:iplc/shandianmao</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6240,7 +8967,6 @@
           <t>推荐站:iplc/shandianmao</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6268,7 +8994,6 @@
           <t>探测10-18; 推荐站:iplc/shandianmao</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6296,7 +9021,6 @@
           <t>探测10-18; 推荐站:iplc/shandianmao</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6324,7 +9048,6 @@
           <t>探测10-18; 推荐站:iplc/shandianmao</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6352,7 +9075,6 @@
           <t>探测10-18; 推荐站:iplc/shandianmao</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6380,7 +9102,6 @@
           <t>探测10-18; 推荐站:iplc/shandianmao</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6408,7 +9129,6 @@
           <t>yaml官网; yaml域名表</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6436,7 +9156,6 @@
           <t>推荐站:iplc/shandianmao</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6464,7 +9183,6 @@
           <t>推荐站:iplc/shandianmao</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6492,7 +9210,6 @@
           <t>推荐站:iplc/shandianmao</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6520,7 +9237,6 @@
           <t>推荐站:iplc/shandianmao</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6548,7 +9264,6 @@
           <t>凭证面板; yaml面板; 探测10-17</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6576,7 +9291,6 @@
           <t>探测10-18; 推荐站:iplc/shandianmao</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6604,7 +9318,6 @@
           <t>yaml域名表</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6632,7 +9345,6 @@
           <t>探测10-18; 推荐站:iplc/shandianmao</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6650,13 +9362,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>凭证面板; 探测10-17</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6684,7 +9394,6 @@
           <t>推荐站:pianyijichang/neko77</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6712,7 +9421,6 @@
           <t>推荐站:pianyijichang/neko77</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6740,7 +9448,6 @@
           <t>凭证面板; 探测10-17</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6758,13 +9465,11 @@
           <t>200 活</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>推荐站:pianyijichang/neko77</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6782,13 +9487,11 @@
           <t>403（CF挡脚本≠死）</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>推荐站:pianyijichang/neko77</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6816,7 +9519,6 @@
           <t>推荐站:pianyijichang/neko77</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6844,7 +9546,6 @@
           <t>推荐站:pianyijichang/neko77</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6872,7 +9573,6 @@
           <t>推荐站:pianyijichang/neko77</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6900,7 +9600,6 @@
           <t>推荐站:pianyijichang/neko77</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6928,7 +9627,6 @@
           <t>推荐站:pianyijichang/neko77</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6956,7 +9654,6 @@
           <t>凭证面板; 探测10-17</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6984,7 +9681,6 @@
           <t>yaml域名表</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7012,7 +9708,6 @@
           <t>推荐站:anliangfufei/flyint</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7040,7 +9735,6 @@
           <t>推荐站:anliangfufei/flyint</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7068,7 +9762,6 @@
           <t>推荐站:anliangfufei/flyint</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7096,7 +9789,6 @@
           <t>凭证面板; 探测10-17; 推荐站:anliangfufei/flyint</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7124,7 +9816,6 @@
           <t>推荐站:anliangfufei/flyint</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7152,7 +9843,6 @@
           <t>推荐站:anliangfufei/flyint</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7180,7 +9870,6 @@
           <t>推荐站:anliangfufei/flyint</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7208,7 +9897,6 @@
           <t>推荐站:anliangfufei/flyint</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7236,7 +9924,6 @@
           <t>推荐站:anliangfufei/flyint</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7264,7 +9951,6 @@
           <t>推荐站:anliangfufei/flyint</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7292,7 +9978,6 @@
           <t>推荐站:pianyijichang/mitce</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7321,7 +10006,6 @@
           <t>凭证面板; 探测10-17; 推荐站:pianyijichang/mitce</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7350,7 +10034,6 @@
           <t>推荐站:pianyijichang/mitce</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7378,7 +10061,6 @@
           <t>推荐站:pianyijichang/mitce</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7406,7 +10088,6 @@
           <t>推荐站:pianyijichang/mitce</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7434,7 +10115,6 @@
           <t>yaml官网; yaml域名表</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7452,13 +10132,11 @@
           <t>200 活</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>凭证面板; yaml面板; 探测10-17</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7486,7 +10164,6 @@
           <t>yaml域名表</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7514,7 +10191,6 @@
           <t>yaml域名表</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7542,7 +10218,6 @@
           <t>yaml域名表</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7570,7 +10245,6 @@
           <t>yaml域名表</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7598,7 +10272,6 @@
           <t>yaml域名表</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7626,7 +10299,6 @@
           <t>推荐站:pianyijichang/liangxinyun</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7654,7 +10326,6 @@
           <t>推荐站:pianyijichang/liangxinyun</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7682,7 +10353,6 @@
           <t>推荐站:pianyijichang/liangxinyun</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7710,7 +10380,6 @@
           <t>凭证面板; 探测10-17; 推荐站:pianyijichang/liangxinyun</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7728,13 +10397,11 @@
           <t>403（CF挡脚本≠死）</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>推荐站:pianyijichang/liangxinyun</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7752,13 +10419,11 @@
           <t>403（CF挡脚本≠死）</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>推荐站:pianyijichang/liangxinyun</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7786,7 +10451,6 @@
           <t>推荐站:pianyijichang/liangxinyun</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7814,7 +10478,6 @@
           <t>推荐站:pianyijichang/liangxinyun</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7842,7 +10505,6 @@
           <t>推荐站:pianyijichang/ktmcloud</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7870,7 +10532,6 @@
           <t>推荐站:pianyijichang/ktmcloud</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7898,7 +10559,6 @@
           <t>推荐站:pianyijichang/ktmcloud</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7926,7 +10586,6 @@
           <t>凭证面板; 探测10-17; 推荐站:pianyijichang/ktmcloud</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7954,7 +10613,6 @@
           <t>推荐站:pianyijichang/ktmcloud</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7982,7 +10640,6 @@
           <t>推荐站:pianyijichang/ktmcloud</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8000,13 +10657,11 @@
           <t>403（CF挡脚本≠死）</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
           <t>推荐站:pianyijichang/ktmcloud</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8024,13 +10679,11 @@
           <t>403（CF挡脚本≠死）</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
           <t>推荐站:pianyijichang/ktmcloud</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8048,13 +10701,11 @@
           <t>403（CF挡脚本≠死）</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
           <t>推荐站:pianyijichang/ktmcloud</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8072,13 +10723,11 @@
           <t>403（CF挡脚本≠死）</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
           <t>推荐站:pianyijichang/ktmcloud</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8096,13 +10745,11 @@
           <t>403（CF挡脚本≠死）</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
           <t>推荐站:pianyijichang/ktmcloud</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8120,13 +10767,11 @@
           <t>403（CF挡脚本≠死）</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>推荐站:pianyijichang/ktmcloud</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8144,13 +10789,11 @@
           <t>403（CF挡脚本≠死）</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
           <t>推荐站:pianyijichang/ktmcloud</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8178,7 +10821,6 @@
           <t>推荐站:pianyijichang/ktmcloud</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8206,7 +10848,6 @@
           <t>推荐站:pianyijichang/ktmcloud</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -8234,7 +10875,6 @@
           <t>推荐站:pianyijichang/ktmcloud</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -8262,7 +10902,6 @@
           <t>推荐站:pianyijichang/ktmcloud</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -8290,7 +10929,6 @@
           <t>推荐站:pianyijichang/ktmcloud</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -8318,7 +10956,6 @@
           <t>推荐站:pianyijichang/ktmcloud</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8346,7 +10983,6 @@
           <t>推荐站:pianyijichang/ktmcloud</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8374,7 +11010,6 @@
           <t>推荐站:pianyijichang/ktmcloud</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8402,7 +11037,6 @@
           <t>推荐站:pianyijichang/ktmcloud</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -8430,7 +11064,6 @@
           <t>推荐站:pianyijichang/ktmcloud</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -8458,7 +11091,6 @@
           <t>推荐站:pianyijichang/ktmcloud</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8486,7 +11118,6 @@
           <t>推荐站:pianyijichang/ktmcloud</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8514,7 +11145,6 @@
           <t>推荐站:pianyijichang/ktmcloud</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8532,7 +11162,6 @@
           <t>502</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
           <t>凭证面板; yaml面板; 探测10-17</t>
@@ -8570,7 +11199,6 @@
           <t>yaml域名表</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8598,7 +11226,6 @@
           <t>yaml官网; yaml域名表</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8626,7 +11253,6 @@
           <t>yaml域名表</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -8654,7 +11280,6 @@
           <t>yaml域名表</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8682,7 +11307,6 @@
           <t>探测10-18; 推荐站:pianyijichang/jinglingxueyuan</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8710,7 +11334,6 @@
           <t>探测10-18; 推荐站:pianyijichang/jinglingxueyuan</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8738,7 +11361,6 @@
           <t>推荐站:pianyijichang/jinglingxueyuan</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8766,7 +11388,6 @@
           <t>探测10-18; 推荐站:pianyijichang/jinglingxueyuan</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8794,7 +11415,6 @@
           <t>凭证面板; 探测10-17</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -8822,7 +11442,6 @@
           <t>探测10-18; 推荐站:pianyijichang/jinglingxueyuan</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -8850,7 +11469,6 @@
           <t>凭证面板; 探测10-17; 推荐站:iplc/oixcloud</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8878,7 +11496,6 @@
           <t>凭证面板; 探测10-17; 推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8906,7 +11523,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8934,7 +11550,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -8962,7 +11577,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -8990,7 +11604,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -9018,7 +11631,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -9046,7 +11658,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -9074,7 +11685,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -9102,7 +11712,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -9130,7 +11739,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -9158,7 +11766,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -9186,7 +11793,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -9214,7 +11820,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -9242,7 +11847,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -9270,7 +11874,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -9298,7 +11901,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -9326,7 +11928,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -9354,7 +11955,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -9382,7 +11982,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -9410,7 +12009,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -9438,7 +12036,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -9466,7 +12063,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -9494,7 +12090,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -9522,7 +12117,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -9550,7 +12144,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -9578,7 +12171,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -9606,7 +12198,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -9634,7 +12225,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -9662,7 +12252,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -9690,7 +12279,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -9718,7 +12306,6 @@
           <t>推荐站:pianyijichang/selom</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -9746,7 +12333,6 @@
           <t>推荐站:pianyijichang/selom</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -9774,7 +12360,6 @@
           <t>凭证面板; 探测10-17; 推荐站:pianyijichang/selom</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -9802,7 +12387,6 @@
           <t>推荐站:pianyijichang/selom</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -9830,7 +12414,6 @@
           <t>推荐站:pianyijichang/selom</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -9858,7 +12441,6 @@
           <t>推荐站:pianyijichang/selom</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -9886,7 +12468,6 @@
           <t>推荐站:pianyijichang/selom</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -9914,7 +12495,6 @@
           <t>推荐站:pianyijichang/selom</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -9942,7 +12522,6 @@
           <t>推荐站:pianyijichang/selom</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -9970,7 +12549,6 @@
           <t>推荐站:pianyijichang/selom</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -9998,7 +12576,6 @@
           <t>推荐站:pianyijichang/selom</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -10026,7 +12603,6 @@
           <t>推荐站:pianyijichang/selom</t>
         </is>
       </c>
-      <c r="F191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -10054,7 +12630,6 @@
           <t>推荐站:pianyijichang/selom</t>
         </is>
       </c>
-      <c r="F192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -10082,7 +12657,6 @@
           <t>推荐站:pianyijichang/muniuyun</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -10110,7 +12684,6 @@
           <t>推荐站:pianyijichang/muniuyun</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -10138,7 +12711,6 @@
           <t>推荐站:pianyijichang/muniuyun</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -10166,7 +12738,6 @@
           <t>推荐站:pianyijichang/muniuyun</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -10194,7 +12765,6 @@
           <t>推荐站:pianyijichang/muniuyun</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -10212,13 +12782,11 @@
           <t>403（CF挡脚本≠死）</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
           <t>推荐站:pianyijichang/muniuyun</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -10236,13 +12804,11 @@
           <t>403（CF挡脚本≠死）</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
           <t>推荐站:pianyijichang/muniuyun</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -10270,7 +12836,6 @@
           <t>推荐站:pianyijichang/muniuyun</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -10298,7 +12863,6 @@
           <t>推荐站:pianyijichang/muniuyun</t>
         </is>
       </c>
-      <c r="F201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -10326,7 +12890,6 @@
           <t>推荐站:pianyijichang/muniuyun</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -10354,7 +12917,6 @@
           <t>推荐站:pianyijichang/muniuyun</t>
         </is>
       </c>
-      <c r="F203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -10382,7 +12944,6 @@
           <t>凭证面板; 探测10-17</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -10410,7 +12971,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -10438,7 +12998,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -10466,7 +13025,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -10494,7 +13052,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -10522,7 +13079,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -10550,7 +13106,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -10578,7 +13133,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -10606,7 +13160,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -10634,7 +13187,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -10662,7 +13214,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -10690,7 +13241,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -10718,7 +13268,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -10746,7 +13295,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -10774,7 +13322,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -10802,7 +13349,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -10830,7 +13376,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -10858,7 +13403,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -10886,7 +13430,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -10914,7 +13457,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -10942,7 +13484,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -10970,7 +13511,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -10998,7 +13538,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -11026,7 +13565,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -11054,7 +13592,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -11082,7 +13619,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -11110,7 +13646,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -11138,7 +13673,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -11166,7 +13700,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -11194,7 +13727,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -11222,7 +13754,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -11240,13 +13771,11 @@
           <t>200 活</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr">
         <is>
           <t>凭证面板; 探测10-17; 推荐站:anliangfufei/mojie</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -11274,7 +13803,6 @@
           <t>推荐站:mojie; 他牌文章引用</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -11302,7 +13830,6 @@
           <t>推荐站:anliangfufei/mojie</t>
         </is>
       </c>
-      <c r="F237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -11320,13 +13847,11 @@
           <t>403（CF挡脚本≠死）</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr">
         <is>
           <t>推荐站:anliangfufei/mojie</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -11354,7 +13879,6 @@
           <t>推荐站:anliangfufei/mojie</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -11383,7 +13907,6 @@
           <t>凭证面板; yaml面板; 探测10-17</t>
         </is>
       </c>
-      <c r="F240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -11411,7 +13934,6 @@
           <t>yaml域名表</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -11439,7 +13961,6 @@
           <t>yaml域名表</t>
         </is>
       </c>
-      <c r="F242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -11467,7 +13988,6 @@
           <t>yaml官网</t>
         </is>
       </c>
-      <c r="F243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -11495,7 +14015,6 @@
           <t>yaml域名表</t>
         </is>
       </c>
-      <c r="F244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -11523,7 +14042,6 @@
           <t>凭证面板; 探测10-17</t>
         </is>
       </c>
-      <c r="F245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -11551,7 +14069,6 @@
           <t>凭证面板; 探测10-17</t>
         </is>
       </c>
-      <c r="F246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -11569,13 +14086,11 @@
           <t>200 活</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
           <t>凭证面板; 探测10-17</t>
         </is>
       </c>
-      <c r="F247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -11593,8 +14108,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
-      <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
         <is>
           <t>本机场无 yaml/凭证/文章来源</t>
@@ -11627,7 +14140,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -11655,7 +14167,6 @@
           <t>凭证面板; 探测10-17</t>
         </is>
       </c>
-      <c r="F250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -11683,7 +14194,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -11711,7 +14221,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -11739,7 +14248,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -11767,7 +14275,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -11795,7 +14302,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -11823,7 +14329,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -11851,7 +14356,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -11879,7 +14383,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -11907,7 +14410,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -11935,7 +14437,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -11963,7 +14464,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -11991,7 +14491,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -12019,7 +14518,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -12047,7 +14545,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -12075,7 +14572,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -12103,7 +14599,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -12131,7 +14626,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -12159,7 +14653,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -12187,7 +14680,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -12215,7 +14707,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -12243,7 +14734,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -12271,7 +14761,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -12299,7 +14788,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -12327,7 +14815,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -12355,7 +14842,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -12383,7 +14869,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -12411,7 +14896,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -12439,7 +14923,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -12467,7 +14950,6 @@
           <t>推荐站:pianyijichang/feiniaoyun</t>
         </is>
       </c>
-      <c r="F279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -12485,13 +14967,11 @@
           <t>200 活</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
           <t>搜索发现</t>
         </is>
       </c>
-      <c r="F280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -12509,13 +14989,11 @@
           <t>503（CF挡脚本≠死）</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
           <t>搜索发现</t>
         </is>
       </c>
-      <c r="F281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -12543,7 +15021,6 @@
           <t>凭证面板; 探测10-17</t>
         </is>
       </c>
-      <c r="F282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -12571,7 +15048,6 @@
           <t>搜索发现</t>
         </is>
       </c>
-      <c r="F283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -12599,7 +15075,6 @@
           <t>搜索发现</t>
         </is>
       </c>
-      <c r="F284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -12627,7 +15102,6 @@
           <t>凭证面板; 探测10-17</t>
         </is>
       </c>
-      <c r="F285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -12655,7 +15129,6 @@
           <t>探测10-18; 推荐站:pianyijichang/hsyun</t>
         </is>
       </c>
-      <c r="F286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -12683,7 +15156,6 @@
           <t>探测10-18; 推荐站:pianyijichang/hsyun</t>
         </is>
       </c>
-      <c r="F287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -12711,7 +15183,6 @@
           <t>推荐站:pianyijichang/hsyun</t>
         </is>
       </c>
-      <c r="F288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -12739,7 +15210,6 @@
           <t>探测10-18; 推荐站:pianyijichang/hsyun</t>
         </is>
       </c>
-      <c r="F289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -12767,7 +15237,6 @@
           <t>推荐站:pianyijichang/hsyun</t>
         </is>
       </c>
-      <c r="F290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -12785,13 +15254,11 @@
           <t>403（CF挡脚本≠死）</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr">
         <is>
           <t>推荐站:pianyijichang/hsyun</t>
         </is>
       </c>
-      <c r="F291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -12809,13 +15276,11 @@
           <t>403（CF挡脚本≠死）</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr">
         <is>
           <t>推荐站:pianyijichang/hsyun</t>
         </is>
       </c>
-      <c r="F292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -12843,7 +15308,6 @@
           <t>凭证面板; 探测10-17</t>
         </is>
       </c>
-      <c r="F293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -12871,7 +15335,6 @@
           <t>探测10-18; 推荐站:pianyijichang/hsyun</t>
         </is>
       </c>
-      <c r="F294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -12899,7 +15362,6 @@
           <t>探测10-18; 推荐站:pianyijichang/hsyun</t>
         </is>
       </c>
-      <c r="F295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -12927,7 +15389,6 @@
           <t>探测10-18; 推荐站:pianyijichang/hsyun</t>
         </is>
       </c>
-      <c r="F296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -12955,7 +15416,6 @@
           <t>探测10-18</t>
         </is>
       </c>
-      <c r="F297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -12983,7 +15443,6 @@
           <t>推荐站:bybw</t>
         </is>
       </c>
-      <c r="F298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -13001,13 +15460,11 @@
           <t>200 活</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr">
         <is>
           <t>探测10-18</t>
         </is>
       </c>
-      <c r="F299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -13035,7 +15492,6 @@
           <t>探测10-18; 推荐站:iplc/bywave</t>
         </is>
       </c>
-      <c r="F300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -13063,7 +15519,6 @@
           <t>yaml域名表; 推荐站:iplc/bywave</t>
         </is>
       </c>
-      <c r="F301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -13091,7 +15546,6 @@
           <t>凭证面板; 探测10-17</t>
         </is>
       </c>
-      <c r="F302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -13119,7 +15573,6 @@
           <t>探测10-18; 推荐站:iplc/bywave</t>
         </is>
       </c>
-      <c r="F303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -13147,7 +15600,6 @@
           <t>推荐站:iplc/bywave</t>
         </is>
       </c>
-      <c r="F304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -13175,7 +15627,6 @@
           <t>探测10-18; 推荐站:iplc/bywave</t>
         </is>
       </c>
-      <c r="F305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -13203,7 +15654,6 @@
           <t>推荐站:iplc/bywave</t>
         </is>
       </c>
-      <c r="F306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -13221,13 +15671,11 @@
           <t>200 活</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
       <c r="E307" t="inlineStr">
         <is>
           <t>探测10-18; 推荐站:pianyijichang/yiyuanjichang</t>
         </is>
       </c>
-      <c r="F307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -13255,7 +15703,6 @@
           <t>凭证面板; 探测10-17</t>
         </is>
       </c>
-      <c r="F308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -13283,7 +15730,6 @@
           <t>探测10-18; 推荐站:pianyijichang/yiyuanjichang</t>
         </is>
       </c>
-      <c r="F309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -13311,7 +15757,6 @@
           <t>探测10-18; 推荐站:pianyijichang/yiyuanjichang</t>
         </is>
       </c>
-      <c r="F310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -13339,7 +15784,6 @@
           <t>探测10-18; 推荐站:pianyijichang/yiyuanjichang</t>
         </is>
       </c>
-      <c r="F311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -13367,7 +15811,6 @@
           <t>推荐站:pianyijichang/yiyuanjichang</t>
         </is>
       </c>
-      <c r="F312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -13395,7 +15838,6 @@
           <t>探测10-18; 推荐站:pianyijichang/yiyuanjichang</t>
         </is>
       </c>
-      <c r="F313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -13423,7 +15865,6 @@
           <t>推荐站:pianyijichang/yiyuanjichang</t>
         </is>
       </c>
-      <c r="F314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -13451,7 +15892,6 @@
           <t>探测10-18; 推荐站:pianyijichang/yiyuanjichang</t>
         </is>
       </c>
-      <c r="F315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -13469,13 +15909,11 @@
           <t>200 活</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
           <t>凭证面板; 探测10-17</t>
         </is>
       </c>
-      <c r="F316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -13503,7 +15941,6 @@
           <t>凭证面板; 探测10-17</t>
         </is>
       </c>
-      <c r="F317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -13531,7 +15968,6 @@
           <t>yaml面板; 探测10-17</t>
         </is>
       </c>
-      <c r="F318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -13559,7 +15995,6 @@
           <t>推荐站:iplc/wandayun</t>
         </is>
       </c>
-      <c r="F319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -13587,7 +16022,6 @@
           <t>推荐站:iplc/wandayun</t>
         </is>
       </c>
-      <c r="F320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -13615,7 +16049,6 @@
           <t>推荐站:iplc/wandayun</t>
         </is>
       </c>
-      <c r="F321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -13643,7 +16076,6 @@
           <t>推荐站:iplc/wandayun</t>
         </is>
       </c>
-      <c r="F322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -13671,7 +16103,6 @@
           <t>yaml官网; yaml域名表; 推荐站:iplc/wandayun</t>
         </is>
       </c>
-      <c r="F323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -13699,7 +16130,6 @@
           <t>推荐站:iplc/wandayun</t>
         </is>
       </c>
-      <c r="F324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -13727,7 +16157,6 @@
           <t>推荐站:iplc/wandayun</t>
         </is>
       </c>
-      <c r="F325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -13755,7 +16184,6 @@
           <t>yaml域名表; 推荐站:iplc/wandayun</t>
         </is>
       </c>
-      <c r="F326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -13783,7 +16211,6 @@
           <t>yaml域名表</t>
         </is>
       </c>
-      <c r="F327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -13811,7 +16238,6 @@
           <t>推荐站:iplc/wandayun</t>
         </is>
       </c>
-      <c r="F328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -13839,7 +16265,6 @@
           <t>推荐站:iplc/wandayun</t>
         </is>
       </c>
-      <c r="F329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -13857,13 +16282,11 @@
           <t>520</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
           <t>推荐站:iplc/wandayun</t>
         </is>
       </c>
-      <c r="F330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -13891,7 +16314,6 @@
           <t>推荐站:iplc/wandayun</t>
         </is>
       </c>
-      <c r="F331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -13919,7 +16341,6 @@
           <t>yaml域名表</t>
         </is>
       </c>
-      <c r="F332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -13947,7 +16368,6 @@
           <t>推荐站:iplc/wandayun</t>
         </is>
       </c>
-      <c r="F333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -13975,7 +16395,6 @@
           <t>凭证面板; 探测10-17</t>
         </is>
       </c>
-      <c r="F334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -14003,7 +16422,6 @@
           <t>推荐站:iplc/wandayun</t>
         </is>
       </c>
-      <c r="F335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -14031,7 +16449,6 @@
           <t>推荐站:iplc/wandayun</t>
         </is>
       </c>
-      <c r="F336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -14059,7 +16476,6 @@
           <t>推荐站:iplc/wandayun</t>
         </is>
       </c>
-      <c r="F337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -14087,7 +16503,6 @@
           <t>推荐站:iplc/wandayun</t>
         </is>
       </c>
-      <c r="F338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -14115,7 +16530,6 @@
           <t>推荐站:iplc/wandayun</t>
         </is>
       </c>
-      <c r="F339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -14143,7 +16557,6 @@
           <t>推荐站:iplc/wandayun</t>
         </is>
       </c>
-      <c r="F340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -14171,7 +16584,6 @@
           <t>推荐站:iplc/wandayun</t>
         </is>
       </c>
-      <c r="F341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -14199,7 +16611,6 @@
           <t>推荐站:iplc/wandayun</t>
         </is>
       </c>
-      <c r="F342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -14227,7 +16638,6 @@
           <t>推荐站:iplc/wandayun</t>
         </is>
       </c>
-      <c r="F343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -14255,7 +16665,6 @@
           <t>推荐站:iplc/wandayun</t>
         </is>
       </c>
-      <c r="F344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -14273,13 +16682,11 @@
           <t>520</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
           <t>推荐站:iplc/wandayun</t>
         </is>
       </c>
-      <c r="F345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -14307,7 +16714,6 @@
           <t>推荐站:iplc/wandayun</t>
         </is>
       </c>
-      <c r="F346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -14335,7 +16741,6 @@
           <t>推荐站:iplc/wandayun</t>
         </is>
       </c>
-      <c r="F347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -14363,7 +16768,6 @@
           <t>推荐站:iplc/qingyunti</t>
         </is>
       </c>
-      <c r="F348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -14391,7 +16795,6 @@
           <t>推荐站:iplc/qingyunti</t>
         </is>
       </c>
-      <c r="F349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -14419,7 +16822,6 @@
           <t>探测10-18; 推荐站:iplc/qingyunti</t>
         </is>
       </c>
-      <c r="F350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -14447,7 +16849,6 @@
           <t>探测10-18; 推荐站:iplc/qingyunti</t>
         </is>
       </c>
-      <c r="F351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -14475,7 +16876,6 @@
           <t>推荐站:iplc/qingyunti</t>
         </is>
       </c>
-      <c r="F352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -14503,7 +16903,6 @@
           <t>探测10-18; 推荐站:iplc/qingyunti</t>
         </is>
       </c>
-      <c r="F353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -14531,7 +16930,6 @@
           <t>探测10-18; 推荐站:iplc/qingyunti</t>
         </is>
       </c>
-      <c r="F354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -14559,7 +16957,6 @@
           <t>推荐站:iplc/qingyunti</t>
         </is>
       </c>
-      <c r="F355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -14587,7 +16984,6 @@
           <t>探测10-18; 推荐站:iplc/qingyunti</t>
         </is>
       </c>
-      <c r="F356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -14615,7 +17011,6 @@
           <t>探测10-18; 推荐站:iplc/qingyunti</t>
         </is>
       </c>
-      <c r="F357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -14643,7 +17038,6 @@
           <t>凭证面板; yaml面板; yaml域名表; 探测10-17</t>
         </is>
       </c>
-      <c r="F358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -14671,7 +17065,6 @@
           <t>搜索发现</t>
         </is>
       </c>
-      <c r="F359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -14699,7 +17092,6 @@
           <t>探测10-18; 推荐站:pianyijichang/muniuyun</t>
         </is>
       </c>
-      <c r="F360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -14727,7 +17119,6 @@
           <t>yaml域名表; 探测10-18; 推荐站:pianyijichang/muniuyun</t>
         </is>
       </c>
-      <c r="F361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -14755,7 +17146,6 @@
           <t>推荐站:pianyijichang/muniuyun</t>
         </is>
       </c>
-      <c r="F362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -14783,7 +17173,6 @@
           <t>探测10-18; 推荐站:pianyijichang/muniuyun</t>
         </is>
       </c>
-      <c r="F363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -14811,7 +17200,6 @@
           <t>yaml官网; 推荐站:pianyijichang/muniuyun</t>
         </is>
       </c>
-      <c r="F364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -14839,7 +17227,6 @@
           <t>凭证面板; yaml面板; 探测10-17; 探测10-18; 推荐站:pianyijichang/muniuyun</t>
         </is>
       </c>
-      <c r="F365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -14867,7 +17254,6 @@
           <t>探测10-18; 推荐站:pianyijichang/muniuyun</t>
         </is>
       </c>
-      <c r="F366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -14895,7 +17281,6 @@
           <t>探测10-18; 推荐站:pianyijichang/muniuyun</t>
         </is>
       </c>
-      <c r="F367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -14923,7 +17308,6 @@
           <t>yaml域名表; 推荐站:pianyijichang/muniuyun</t>
         </is>
       </c>
-      <c r="F368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -14951,7 +17335,6 @@
           <t>探测10-18; 推荐站:pianyijichang/muniuyun</t>
         </is>
       </c>
-      <c r="F369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -14979,7 +17362,6 @@
           <t>探测10-18; 推荐站:pianyijichang/muniuyun</t>
         </is>
       </c>
-      <c r="F370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -15007,7 +17389,6 @@
           <t>yaml域名表</t>
         </is>
       </c>
-      <c r="F371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -15036,7 +17417,6 @@
           <t>凭证面板; 探测10-17</t>
         </is>
       </c>
-      <c r="F372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -15054,13 +17434,11 @@
           <t>200 活</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr">
         <is>
           <t>推荐站:pianyijichang/yiyuanjichang</t>
         </is>
       </c>
-      <c r="F373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -15078,13 +17456,11 @@
           <t>403（CF挡脚本≠死）</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr"/>
       <c r="E374" t="inlineStr">
         <is>
           <t>推荐站:pianyijichang/yiyuanjichang</t>
         </is>
       </c>
-      <c r="F374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -15102,13 +17478,11 @@
           <t>403（CF挡脚本≠死）</t>
         </is>
       </c>
-      <c r="D375" t="inlineStr"/>
       <c r="E375" t="inlineStr">
         <is>
           <t>推荐站:pianyijichang/yiyuanjichang</t>
         </is>
       </c>
-      <c r="F375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -15126,13 +17500,11 @@
           <t>403（CF挡脚本≠死）</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
           <t>推荐站:pianyijichang/yiyuanjichang</t>
         </is>
       </c>
-      <c r="F376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -15160,7 +17532,6 @@
           <t>推荐站:pianyijichang/yiyuanjichang</t>
         </is>
       </c>
-      <c r="F377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -15188,7 +17559,6 @@
           <t>推荐站:pianyijichang/yiyuanjichang</t>
         </is>
       </c>
-      <c r="F378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -15216,7 +17586,6 @@
           <t>推荐站:pianyijichang/yiyuanjichang</t>
         </is>
       </c>
-      <c r="F379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -15244,7 +17613,6 @@
           <t>推荐站:pianyijichang/yiyuanjichang</t>
         </is>
       </c>
-      <c r="F380" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F380"/>
@@ -15252,7 +17620,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15575,7 +17943,6 @@
           <t>免费,试用,体验,邀请码</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>14</v>
       </c>
